--- a/src/nodes/HPC/compressor_stage_4_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_4_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00099075003731379971</v>
       </c>
       <c r="B2">
-        <v>0.0010861439209312776</v>
+        <v>0.0010274915187223007</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0019815000746275994</v>
       </c>
       <c r="B3">
-        <v>0.001614388346338938</v>
+        <v>0.001533543143294132</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0029722501119414</v>
       </c>
       <c r="B4">
-        <v>0.0020556068693897132</v>
+        <v>0.0019576415057001246</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0039630001492551989</v>
       </c>
       <c r="B5">
-        <v>0.0024360200628714638</v>
+        <v>0.002324263458662467</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0049537501865689988</v>
       </c>
       <c r="B6">
-        <v>0.0027663445407792617</v>
+        <v>0.0026434152233890617</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0059445002238828</v>
       </c>
       <c r="B7">
-        <v>0.0030527130356756476</v>
+        <v>0.0029208243907084346</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0069352502611965986</v>
       </c>
       <c r="B8">
-        <v>0.0032987467855261354</v>
+        <v>0.0031598743217569445</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0079260002985103977</v>
       </c>
       <c r="B9">
-        <v>0.0035100798586809247</v>
+        <v>0.0033658266532480352</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0089167503358241976</v>
       </c>
       <c r="B10">
-        <v>0.0036927901757554862</v>
+        <v>0.0035443571080813973</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.0099075003731379976</v>
       </c>
       <c r="B11">
-        <v>0.0038527182360417042</v>
+        <v>0.0037009194783246329</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.010898250410451798</v>
       </c>
       <c r="B12">
-        <v>0.0039929939500244691</v>
+        <v>0.003838437508077597</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.0118890004477656</v>
       </c>
       <c r="B13">
-        <v>0.0041061422942842872</v>
+        <v>0.0039499366804012443</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.012879750485079397</v>
       </c>
       <c r="B14">
-        <v>0.0041877005397468435</v>
+        <v>0.0040312537874422575</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.013870500522393197</v>
       </c>
       <c r="B15">
-        <v>0.0042558600686229088</v>
+        <v>0.0040993691187291188</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.014861250559706996</v>
       </c>
       <c r="B16">
-        <v>0.0043273058644148731</v>
+        <v>0.0041698568492607845</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.015852000597020795</v>
       </c>
       <c r="B17">
-        <v>0.0043900432045065061</v>
+        <v>0.0042315231985362977</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.0168427506343346</v>
       </c>
       <c r="B18">
-        <v>0.0044285764194361742</v>
+        <v>0.0042699066517326223</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.017833500671648395</v>
       </c>
       <c r="B19">
-        <v>0.0044420857584792613</v>
+        <v>0.0042842427122383106</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.018824250708962195</v>
       </c>
       <c r="B20">
-        <v>0.0044334204505954026</v>
+        <v>0.004277191137994814</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.019815000746275995</v>
       </c>
       <c r="B21">
-        <v>0.0044054297247442357</v>
+        <v>0.004251411686943582</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.020805750783589795</v>
       </c>
       <c r="B22">
-        <v>0.0043604547394737276</v>
+        <v>0.0042090897618341609</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.021796500820903595</v>
       </c>
       <c r="B23">
-        <v>0.0042988043716851686</v>
+        <v>0.0041505133446484805</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.0227872508582174</v>
       </c>
       <c r="B24">
-        <v>0.0042202794278681788</v>
+        <v>0.0040754960621765673</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.0237780008955312</v>
       </c>
       <c r="B25">
-        <v>0.0041246807145123776</v>
+        <v>0.0039838515412084453</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.024768750932844995</v>
       </c>
       <c r="B26">
-        <v>0.00401172368401834</v>
+        <v>0.0038753135927388767</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.025759500970158795</v>
       </c>
       <c r="B27">
-        <v>0.0038807823724304573</v>
+        <v>0.0037492967645815643</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.026750251007472595</v>
       </c>
       <c r="B28">
-        <v>0.0037311454617040734</v>
+        <v>0.0036051357887549504</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.027741001044786395</v>
       </c>
       <c r="B29">
-        <v>0.0035621016337945332</v>
+        <v>0.0034421653972774744</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.028731751082100198</v>
       </c>
       <c r="B30">
-        <v>0.0033733145243884494</v>
+        <v>0.0032600701207551085</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.029722501119413991</v>
       </c>
       <c r="B31">
-        <v>0.0031659475840975088</v>
+        <v>0.003059933684143958</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.030713251156727794</v>
       </c>
       <c r="B32">
-        <v>0.0029415392172646624</v>
+        <v>0.0028431896109876575</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.031704001194041591</v>
       </c>
       <c r="B33">
-        <v>0.0027016278282328641</v>
+        <v>0.002611271424829845</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.032694751231355394</v>
       </c>
       <c r="B34">
-        <v>0.0024471403403076193</v>
+        <v>0.0023650417592058172</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.0336855012686692</v>
       </c>
       <c r="B35">
-        <v>0.0021765577526446471</v>
+        <v>0.0021030796876175127</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.034676251305982994</v>
       </c>
       <c r="B36">
-        <v>0.0018877495833622209</v>
+        <v>0.0018233933935585312</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.035667001343296791</v>
       </c>
       <c r="B37">
-        <v>0.0015785853505786093</v>
+        <v>0.0015239910605224696</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.036657751380610594</v>
       </c>
       <c r="B38">
-        <v>0.0012454383513683706</v>
+        <v>0.0012014842312454367</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.03764850141792439</v>
       </c>
       <c r="B39">
-        <v>0.00087869699863120149</v>
+        <v>0.0008468978854335778</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.038639251455238194</v>
       </c>
       <c r="B40">
-        <v>0.00046725348422308339</v>
+        <v>0.00044986036203554678</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.038639251455238194</v>
       </c>
       <c r="B43">
-        <v>-5.45401814030125E-05</v>
+        <v>-3.7147059215475888E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.03764850141792439</v>
       </c>
       <c r="B44">
-        <v>-7.5276397297508141E-05</v>
+        <v>-4.347728409988441E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.036657751380610594</v>
       </c>
       <c r="B45">
-        <v>-7.3185252319644438E-05</v>
+        <v>-2.9231132196710584E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.035667001343296791</v>
       </c>
       <c r="B46">
-        <v>-5.92433511055793E-05</v>
+        <v>-4.649061049439692E-06</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.034676251305982994</v>
       </c>
       <c r="B47">
-        <v>-4.2936110748458551E-05</v>
+        <v>2.1420079055230784E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.0336855012686692</v>
       </c>
       <c r="B48">
-        <v>-2.7784198169380062E-05</v>
+        <v>4.5693866857754257E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.032694751231355394</v>
       </c>
       <c r="B49">
-        <v>-1.5817092746429465E-05</v>
+        <v>6.6281488355372293E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.031704001194041591</v>
       </c>
       <c r="B50">
-        <v>-9.0642738576926E-06</v>
+        <v>8.12921295453261E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.030713251156727794</v>
       </c>
       <c r="B51">
-        <v>-8.9489710454841319E-06</v>
+        <v>8.9400635231520886E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.029722501119413991</v>
       </c>
       <c r="B52">
-        <v>-1.4469414509034223E-05</v>
+        <v>9.1544485444517283E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.028731751082100198</v>
       </c>
       <c r="B53">
-        <v>-2.4017584611801884E-05</v>
+        <v>8.9226819021539827E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.027741001044786395</v>
       </c>
       <c r="B54">
-        <v>-3.5985461717246273E-05</v>
+        <v>8.3950774799812993E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.026750251007472595</v>
       </c>
       <c r="B55">
-        <v>-4.9144726769617519E-05</v>
+        <v>7.6864946179505461E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.025759500970158795</v>
       </c>
       <c r="B56">
-        <v>-6.3785863036330362E-05</v>
+        <v>6.7699744812562581E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.024768750932844995</v>
       </c>
       <c r="B57">
-        <v>-8.0579054365590672E-05</v>
+        <v>5.58310369138738E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.0237780008955312</v>
       </c>
       <c r="B58">
-        <v>-0.0001001944846056042</v>
+        <v>4.063468869832869E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.0227872508582174</v>
       </c>
       <c r="B59">
-        <v>-0.00012322154288017193</v>
+        <v>2.156182281143996E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.021796500820903595</v>
       </c>
       <c r="B60">
-        <v>-0.0001499264394154744</v>
+        <v>-1.6354123787860329E-06</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.020805750783589795</v>
       </c>
       <c r="B61">
-        <v>-0.000180494589713287</v>
+        <v>-2.91296120737196E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.019815000746275995</v>
       </c>
       <c r="B62">
-        <v>-0.00021511140927538532</v>
+        <v>-6.1093371474731055E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.018824250708962195</v>
       </c>
       <c r="B63">
-        <v>-0.00025345892742225707</v>
+        <v>-9.7229614821668173E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.017833500671648395</v>
       </c>
       <c r="B64">
-        <v>-0.00029320562874923935</v>
+        <v>-0.00013536258250828912</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.0168427506343346</v>
       </c>
       <c r="B65">
-        <v>-0.00033151661167038135</v>
+        <v>-0.00017284684396682925</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.015852000597020795</v>
       </c>
       <c r="B66">
-        <v>-0.00036555697459973247</v>
+        <v>-0.00020703696862952434</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.014861250559706996</v>
       </c>
       <c r="B67">
-        <v>-0.00039616459020778088</v>
+        <v>-0.00023871557505369229</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.013870500522393197</v>
       </c>
       <c r="B68">
-        <v>-0.00043886842819077052</v>
+        <v>-0.00028237747829698112</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.012879750485079397</v>
       </c>
       <c r="B69">
-        <v>-0.00050570202939072143</v>
+        <v>-0.00034925527708613575</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.0118890004477656</v>
       </c>
       <c r="B70">
-        <v>-0.00058002612220699982</v>
+        <v>-0.00042382050832395676</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.010898250410451798</v>
       </c>
       <c r="B71">
-        <v>-0.00064369930838169406</v>
+        <v>-0.00048914286643482181</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.0099075003731379976</v>
       </c>
       <c r="B72">
-        <v>-0.00070124449547042972</v>
+        <v>-0.00054944573775335837</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0089167503358241976</v>
       </c>
       <c r="B73">
-        <v>-0.00076020185446717785</v>
+        <v>-0.00061176878679308885</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0079260002985103977</v>
       </c>
       <c r="B74">
-        <v>-0.00081751630430575324</v>
+        <v>-0.00067326309887286379</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0069352502611965986</v>
       </c>
       <c r="B75">
-        <v>-0.00086742712754958855</v>
+        <v>-0.00072855466378039758</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0059445002238828</v>
       </c>
       <c r="B76">
-        <v>-0.00090394631334074342</v>
+        <v>-0.00077205766837353028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0049537501865689988</v>
       </c>
       <c r="B77">
-        <v>-0.00092153498092675367</v>
+        <v>-0.00079860566353655293</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0039630001492551989</v>
       </c>
       <c r="B78">
-        <v>-0.00091667806339843384</v>
+        <v>-0.00080492145918943713</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0029722501119414</v>
       </c>
       <c r="B79">
-        <v>-0.00088335404129794221</v>
+        <v>-0.00078538867760835358</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0019815000746275994</v>
       </c>
       <c r="B80">
-        <v>-0.000810967745005243</v>
+        <v>-0.000730122541960437</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00099075003731379971</v>
       </c>
       <c r="B81">
-        <v>-0.00067342814533803068</v>
+        <v>-0.00061477574312905376</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.001148819359376914</v>
       </c>
       <c r="B2">
-        <v>0.00053429660188938249</v>
+        <v>0.00041697916890981207</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.002297638718753828</v>
       </c>
       <c r="B3">
-        <v>0.000798716252746195</v>
+        <v>0.00063700843972030053</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0034464580781307427</v>
       </c>
       <c r="B4">
-        <v>0.0010207326278441015</v>
+        <v>0.00082478080735390021</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.004595277437507656</v>
       </c>
       <c r="B5">
-        <v>0.001212989764947692</v>
+        <v>0.000989452494000132</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.00574409679688457</v>
       </c>
       <c r="B6">
-        <v>0.0013806426255663247</v>
+        <v>0.001134757522637976</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0068929161562614853</v>
       </c>
       <c r="B7">
-        <v>0.0015266334627465688</v>
+        <v>0.0012628277756141296</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0080417355156384</v>
       </c>
       <c r="B8">
-        <v>0.0016526920800622273</v>
+        <v>0.001374917251626363</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.009190554875015312</v>
       </c>
       <c r="B9">
-        <v>0.0017615228591157559</v>
+        <v>0.0014729853888146498</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.010339374234392226</v>
       </c>
       <c r="B10">
-        <v>0.0018560456262925768</v>
+        <v>0.0015591475315348867</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.011488193593769141</v>
       </c>
       <c r="B11">
-        <v>0.0019390674090813216</v>
+        <v>0.0016354372095644654</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.012637012953146055</v>
       </c>
       <c r="B12">
-        <v>0.0020120865614218905</v>
+        <v>0.001702940399683133</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.013785832312522971</v>
       </c>
       <c r="B13">
-        <v>0.0020714795419560453</v>
+        <v>0.0017590346812585624</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.014934651671899883</v>
       </c>
       <c r="B14">
-        <v>0.002115079107251395</v>
+        <v>0.0018021519177908491</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0160834710312768</v>
       </c>
       <c r="B15">
-        <v>0.0021516651008770685</v>
+        <v>0.0018386495067218469</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.017232290390653712</v>
       </c>
       <c r="B16">
-        <v>0.0021892903519744496</v>
+        <v>0.0018743584210157542</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.018381109750030624</v>
       </c>
       <c r="B17">
-        <v>0.0022221525449724151</v>
+        <v>0.001905078401784387</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.01952992910940754</v>
       </c>
       <c r="B18">
-        <v>0.0022427589211323367</v>
+        <v>0.0019253852222321339</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.020678748468784452</v>
       </c>
       <c r="B19">
-        <v>0.0022507100937580681</v>
+        <v>0.0019349900157860582</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.021827567828161368</v>
       </c>
       <c r="B20">
-        <v>0.0022473800191640824</v>
+        <v>0.001934887755928891</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.022976387187538281</v>
       </c>
       <c r="B21">
-        <v>0.0022341426536648529</v>
+        <v>0.0019260734161433645</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.024125206546915197</v>
       </c>
       <c r="B22">
-        <v>0.0022121273425679939</v>
+        <v>0.0019093647966041693</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.025274025906292109</v>
       </c>
       <c r="B23">
-        <v>0.0021814849871536804</v>
+        <v>0.0018848710042538351</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.026422845265669025</v>
       </c>
       <c r="B24">
-        <v>0.0021421218776952276</v>
+        <v>0.0018525239727268513</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.027571664625045941</v>
       </c>
       <c r="B25">
-        <v>0.0020939443044659511</v>
+        <v>0.0018122556356577068</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.02872048398442285</v>
       </c>
       <c r="B26">
-        <v>0.0020368181591957869</v>
+        <v>0.0017639686059175363</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.029869303343799766</v>
       </c>
       <c r="B27">
-        <v>0.0019704477394411504</v>
+        <v>0.0017074482133240493</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.031018122703176682</v>
       </c>
       <c r="B28">
-        <v>0.0018944969442150784</v>
+        <v>0.0016424504669316008</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.0321669420625536</v>
       </c>
       <c r="B29">
-        <v>0.0018086296725306071</v>
+        <v>0.0015687313757945451</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.033315761421930511</v>
       </c>
       <c r="B30">
-        <v>0.0017126918620798059</v>
+        <v>0.001486178671942598</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.034464580781307423</v>
       </c>
       <c r="B31">
-        <v>0.0016072576052708805</v>
+        <v>0.0013952069793069179</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.035613400140684336</v>
       </c>
       <c r="B32">
-        <v>0.0014930830331910672</v>
+        <v>0.0012963626447940219</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.036762219500061248</v>
       </c>
       <c r="B33">
-        <v>0.0013709242769276049</v>
+        <v>0.0011901920153104286</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.037911038859438168</v>
       </c>
       <c r="B34">
-        <v>0.0012412430218204556</v>
+        <v>0.0010770281828133279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.03905985821881508</v>
       </c>
       <c r="B35">
-        <v>0.0011033231702204786</v>
+        <v>0.00095635121946259494</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.040208677578191993</v>
       </c>
       <c r="B36">
-        <v>0.00095615417873125838</v>
+        <v>0.00082742794246877722</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.041357496937568905</v>
       </c>
       <c r="B37">
-        <v>0.00079872550395637687</v>
+        <v>0.0006895251690424199</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.042506316296945824</v>
       </c>
       <c r="B38">
-        <v>0.00062930467899829467</v>
+        <v>0.0005413869749062184</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.043655135656322737</v>
       </c>
       <c r="B39">
-        <v>0.00044327154295497695</v>
+        <v>0.00037966646983145859</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.044803955015699649</v>
       </c>
       <c r="B40">
-        <v>0.00023528401142326462</v>
+        <v>0.00020049402210157416</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.045952774375076562</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>7.9715356494710763E-20</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.044803955015699649</v>
       </c>
       <c r="B43">
-        <v>-1.6817360473042514E-05</v>
+        <v>1.7972628848647864E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.043655135656322737</v>
       </c>
       <c r="B44">
-        <v>-1.763478402704014E-05</v>
+        <v>4.5970289096478211E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.042506316296945824</v>
       </c>
       <c r="B45">
-        <v>-7.7801332631280429E-06</v>
+        <v>8.0137570828948273E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.041357496937568905</v>
       </c>
       <c r="B46">
-        <v>7.418729217558488E-06</v>
+        <v>0.0001166190641315154</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.040208677578191993</v>
       </c>
       <c r="B47">
-        <v>2.335536523501822E-05</v>
+        <v>0.00015208160149749933</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.03905985821881508</v>
       </c>
       <c r="B48">
-        <v>3.8309034293786075E-05</v>
+        <v>0.00018528098505166964</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.037911038859438168</v>
       </c>
       <c r="B49">
-        <v>5.1280420319531218E-05</v>
+        <v>0.00021549525932665876</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.036762219500061248</v>
       </c>
       <c r="B50">
-        <v>6.1270207237922638E-05</v>
+        <v>0.00024200246885509879</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.035613400140684336</v>
       </c>
       <c r="B51">
-        <v>6.7572972342912644E-05</v>
+        <v>0.00026429336073995795</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.034464580781307423</v>
       </c>
       <c r="B52">
-        <v>7.06588664015866E-05</v>
+        <v>0.00028270949236554912</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.033315761421930511</v>
       </c>
       <c r="B53">
-        <v>7.1291933549313136E-05</v>
+        <v>0.00029780512368652109</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.0321669420625536</v>
       </c>
       <c r="B54">
-        <v>7.0236217921460916E-05</v>
+        <v>0.00031013451465752303</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.031018122703176682</v>
       </c>
       <c r="B55">
-        <v>6.80731957840769E-05</v>
+        <v>0.00032011967306755509</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.029869303343799766</v>
       </c>
       <c r="B56">
-        <v>6.46540719259214E-05</v>
+        <v>0.000327653598043023</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.02872048398442285</v>
       </c>
       <c r="B57">
-        <v>5.9647483266433043E-05</v>
+        <v>0.0003324970365446839</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.027571664625045941</v>
       </c>
       <c r="B58">
-        <v>5.2722066725050514E-05</v>
+        <v>0.0003344107355332948</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.026422845265669025</v>
       </c>
       <c r="B59">
-        <v>4.3586334446123037E-05</v>
+        <v>0.00033318423941449944</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.025274025906292109</v>
       </c>
       <c r="B60">
-        <v>3.2108299473642626E-05</v>
+        <v>0.00032872228237348775</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.024125206546915197</v>
       </c>
       <c r="B61">
-        <v>1.8195850076511927E-05</v>
+        <v>0.00032095839604033636</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.022976387187538281</v>
       </c>
       <c r="B62">
-        <v>1.7568745236335778E-06</v>
+        <v>0.00030982611204512174</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.021827567828161368</v>
       </c>
       <c r="B63">
-        <v>-1.70566709459977E-05</v>
+        <v>0.00029543559228919326</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.020678748468784452</v>
       </c>
       <c r="B64">
-        <v>-3.7116558213019172E-05</v>
+        <v>0.00027860351975899083</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.01952992910940754</v>
       </c>
       <c r="B65">
-        <v>-5.7050491187975911E-05</v>
+        <v>0.00026032320771222727</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.018381109750030624</v>
       </c>
       <c r="B66">
-        <v>-7.5486173781413171E-05</v>
+        <v>0.0002415879694066151</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.017232290390653712</v>
       </c>
       <c r="B67">
-        <v>-9.2825089755226221E-05</v>
+        <v>0.00022210684120346893</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0160834710312768</v>
       </c>
       <c r="B68">
-        <v>-0.00011656384227671107</v>
+        <v>0.00019645175187851048</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.014934651671899883</v>
       </c>
       <c r="B69">
-        <v>-0.00015250922217285094</v>
+        <v>0.000160417967287695</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.013785832312522971</v>
       </c>
       <c r="B70">
-        <v>-0.00019261365150397691</v>
+        <v>0.00011983120919350621</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.012637012953146055</v>
       </c>
       <c r="B71">
-        <v>-0.00022810301639519275</v>
+        <v>8.1043145343564715E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.011488193593769141</v>
       </c>
       <c r="B72">
-        <v>-0.00026115142799734427</v>
+        <v>4.2478771519511556E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.010339374234392226</v>
       </c>
       <c r="B73">
-        <v>-0.00029538984296604388</v>
+        <v>1.5082517916456923E-06</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.009190554875015312</v>
       </c>
       <c r="B74">
-        <v>-0.00032932837495022814</v>
+        <v>-4.0790904649122432E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0080417355156384</v>
       </c>
       <c r="B75">
-        <v>-0.00036016899555997659</v>
+        <v>-8.2394167124112534E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0068929161562614853</v>
       </c>
       <c r="B76">
-        <v>-0.00038500195125661606</v>
+        <v>-0.00012119626412417656</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.00574409679688457</v>
       </c>
       <c r="B77">
-        <v>-0.00040113348261011444</v>
+        <v>-0.00015524837968176582</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.004595277437507656</v>
       </c>
       <c r="B78">
-        <v>-0.00040684553177375667</v>
+        <v>-0.00018330826082619669</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0034464580781307427</v>
       </c>
       <c r="B79">
-        <v>-0.00039920810034576432</v>
+        <v>-0.0002032562798555629</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.002297638718753828</v>
       </c>
       <c r="B80">
-        <v>-0.00037307949381825718</v>
+        <v>-0.00021137168079236288</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.001148819359376914</v>
       </c>
       <c r="B81">
-        <v>-0.00031582972404953393</v>
+        <v>-0.00019851229106996349</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0012879750485079399</v>
       </c>
       <c r="B2">
-        <v>0.00035892199133778877</v>
+        <v>0.00026361183774820123</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0025759500970158797</v>
       </c>
       <c r="B3">
-        <v>0.00053634916040540444</v>
+        <v>0.00040497570545759465</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.00386392514552382</v>
       </c>
       <c r="B4">
-        <v>0.00068529470186655969</v>
+        <v>0.00052610098587097833</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0051519001940317595</v>
       </c>
       <c r="B5">
-        <v>0.0008142609136027035</v>
+        <v>0.00063265643176308394</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0064398752425396987</v>
       </c>
       <c r="B6">
-        <v>0.00092671253234983067</v>
+        <v>0.00072695239159075472</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.00772785029104764</v>
       </c>
       <c r="B7">
-        <v>0.0010246260781724551</v>
+        <v>0.00081030703010073367</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.00901582533955558</v>
       </c>
       <c r="B8">
-        <v>0.0011091625952949864</v>
+        <v>0.000883494841670051</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.010303800388063519</v>
       </c>
       <c r="B9">
-        <v>0.0011821389511075784</v>
+        <v>0.000947727492279133</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.011591775436571458</v>
       </c>
       <c r="B10">
-        <v>0.0012455170581286668</v>
+        <v>0.0010043133231582722</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.012879750485079397</v>
       </c>
       <c r="B11">
-        <v>0.0013011831862240718</v>
+        <v>0.001054510204933831</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.014167725533587338</v>
       </c>
       <c r="B12">
-        <v>0.0013501434059080785</v>
+        <v>0.0010989891877444113</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.015455700582095279</v>
       </c>
       <c r="B13">
-        <v>0.0013899586329414483</v>
+        <v>0.0011361245103815036</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.016743675630603218</v>
       </c>
       <c r="B14">
-        <v>0.001419169521259437</v>
+        <v>0.0011649435487644853</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.018031650679111159</v>
       </c>
       <c r="B15">
-        <v>0.0014436808322488013</v>
+        <v>0.0011893830386713934</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.019319625727619097</v>
       </c>
       <c r="B16">
-        <v>0.0014689083849914058</v>
+        <v>0.001213053735366012</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.020607600776127038</v>
       </c>
       <c r="B17">
-        <v>0.0014909481218980446</v>
+        <v>0.0012333531121964565</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.021895575824634979</v>
       </c>
       <c r="B18">
-        <v>0.0015047589989959935</v>
+        <v>0.0012469206264777218</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.023183550873142916</v>
       </c>
       <c r="B19">
-        <v>0.0015100719034495305</v>
+        <v>0.0012535769533079865</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.024471525921650857</v>
       </c>
       <c r="B20">
-        <v>0.0015078107052071824</v>
+        <v>0.0012539380722312258</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.025759500970158795</v>
       </c>
       <c r="B21">
-        <v>0.0014988992742174774</v>
+        <v>0.0012486199627914146</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.027047476018666736</v>
       </c>
       <c r="B22">
-        <v>0.0014840970537241666</v>
+        <v>0.00123812896505987</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.028335451067174677</v>
       </c>
       <c r="B23">
-        <v>0.0014635057801518957</v>
+        <v>0.0012225328612172773</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.029623426115682618</v>
       </c>
       <c r="B24">
-        <v>0.0014370627632205345</v>
+        <v>0.0012017897939716655</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.030911401164190559</v>
       </c>
       <c r="B25">
-        <v>0.0014047053126499526</v>
+        <v>0.0011758579060310618</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.032199376212698493</v>
       </c>
       <c r="B26">
-        <v>0.0013663436764398552</v>
+        <v>0.0011446772781107254</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.033487351261206437</v>
       </c>
       <c r="B27">
-        <v>0.0013217798557092885</v>
+        <v>0.0011081157429548376</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.034775326309714374</v>
       </c>
       <c r="B28">
-        <v>0.0012707887898571353</v>
+        <v>0.0010660230713148105</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.036063301358222319</v>
       </c>
       <c r="B29">
-        <v>0.0012131454182822779</v>
+        <v>0.0010182490339420568</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.037351276406730256</v>
       </c>
       <c r="B30">
-        <v>0.0011487472487973253</v>
+        <v>0.000964725092893145</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.038639251455238194</v>
       </c>
       <c r="B31">
-        <v>0.0010779820628697933</v>
+        <v>0.000905709475445272</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.039927226503746131</v>
       </c>
       <c r="B32">
-        <v>0.0010013602103809234</v>
+        <v>0.00084154210018079045</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.041215201552254076</v>
       </c>
       <c r="B33">
-        <v>0.00091939204121195865</v>
+        <v>0.00077256288568205338</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.042503176600762013</v>
       </c>
       <c r="B34">
-        <v>0.00083238995894332134</v>
+        <v>0.00069897976465289348</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.043791151649269958</v>
       </c>
       <c r="B35">
-        <v>0.0007398745819521545</v>
+        <v>0.00062047272628306131</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.045079126697777888</v>
       </c>
       <c r="B36">
-        <v>0.00064116858231478191</v>
+        <v>0.00053658977388378667</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.046367101746285833</v>
       </c>
       <c r="B37">
-        <v>0.00053559463210752574</v>
+        <v>0.0004468789107662988</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.04765507679479377</v>
       </c>
       <c r="B38">
-        <v>0.00042198989142067637</v>
+        <v>0.00035056444622090879</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.048943051843301714</v>
       </c>
       <c r="B39">
-        <v>0.00029724947240039005</v>
+        <v>0.00024557591345425158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.050231026891809652</v>
       </c>
       <c r="B40">
-        <v>0.00015778297520678997</v>
+        <v>0.00012951915165204311</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.051519001940317589</v>
       </c>
       <c r="B41">
-        <v>-4.46856110623818E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.051519001940317589</v>
       </c>
       <c r="B42">
-        <v>2.7928506913988624E-21</v>
+        <v>-5.5857013827977249E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.050231026891809652</v>
       </c>
       <c r="B43">
-        <v>-1.1799966121691186E-05</v>
+        <v>1.6463857433055693E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.048943051843301714</v>
       </c>
       <c r="B44">
-        <v>-1.2791881276440624E-05</v>
+        <v>3.8881677669697846E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.04765507679479377</v>
       </c>
       <c r="B45">
-        <v>-6.5627797779286174E-06</v>
+        <v>6.48626654218389E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.046367101746285833</v>
       </c>
       <c r="B46">
-        <v>3.3003040601644429E-06</v>
+        <v>9.2016025401391353E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.045079126697777888</v>
       </c>
       <c r="B47">
-        <v>1.3695731728811105E-05</v>
+        <v>0.00011827454015980625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.043791151649269958</v>
       </c>
       <c r="B48">
-        <v>2.3463447937595662E-05</v>
+        <v>0.00014286530360668886</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.042503176600762013</v>
       </c>
       <c r="B49">
-        <v>3.1928793200755461E-05</v>
+        <v>0.00016533898749118313</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.041215201552254076</v>
       </c>
       <c r="B50">
-        <v>3.8417108032527709E-05</v>
+        <v>0.00018524626356243289</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.039927226503746131</v>
       </c>
       <c r="B51">
-        <v>4.2451549180125668E-05</v>
+        <v>0.00020226965938025866</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.038639251455238194</v>
       </c>
       <c r="B52">
-        <v>4.4346538322666532E-05</v>
+        <v>0.00021661912574718768</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.037351276406730256</v>
       </c>
       <c r="B53">
-        <v>4.4614313372243509E-05</v>
+        <v>0.00022863646927642387</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.036063301358222319</v>
       </c>
       <c r="B54">
-        <v>4.3767112240949793E-05</v>
+        <v>0.00023866349658117122</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.034775326309714374</v>
       </c>
       <c r="B55">
-        <v>4.2194478603186016E-05</v>
+        <v>0.000246960197145511</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.033487351261206437</v>
       </c>
       <c r="B56">
-        <v>3.9795179182582631E-05</v>
+        <v>0.00025345929193703372</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.032199376212698493</v>
       </c>
       <c r="B57">
-        <v>3.6345286465077508E-05</v>
+        <v>0.00025801168479420723</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.030911401164190559</v>
       </c>
       <c r="B58">
-        <v>3.1620872936608556E-05</v>
+        <v>0.00026046827955549933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.029623426115682618</v>
       </c>
       <c r="B59">
-        <v>2.5424947727320642E-05</v>
+        <v>0.00026069791697618975</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.028335451067174677</v>
       </c>
       <c r="B60">
-        <v>1.766826654418671E-05</v>
+        <v>0.000258641185478805</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.027047476018666736</v>
       </c>
       <c r="B61">
-        <v>8.2885217383867123E-06</v>
+        <v>0.00025425661040268349</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.025759500970158795</v>
       </c>
       <c r="B62">
-        <v>-2.776594338899398E-06</v>
+        <v>0.0002475027170871635</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.024471525921650857</v>
       </c>
       <c r="B63">
-        <v>-1.5425092648556916E-05</v>
+        <v>0.00023844754032739971</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.023183550873142916</v>
       </c>
       <c r="B64">
-        <v>-2.8897797399732285E-05</v>
+        <v>0.00022759715274181156</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.021895575824634979</v>
       </c>
       <c r="B65">
-        <v>-4.2271236113637115E-05</v>
+        <v>0.00021556713640463472</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.020607600776127038</v>
       </c>
       <c r="B66">
-        <v>-5.4621936311483117E-05</v>
+        <v>0.00020297307339010488</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.019319625727619097</v>
       </c>
       <c r="B67">
-        <v>-6.6219512760956861E-05</v>
+        <v>0.00018963513686443698</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.018031650679111159</v>
       </c>
       <c r="B68">
-        <v>-8.2105929215644534E-05</v>
+        <v>0.00017219186436176316</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.016743675630603218</v>
       </c>
       <c r="B69">
-        <v>-0.0001061863137102716</v>
+        <v>0.00014803965878467989</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.015455700582095279</v>
       </c>
       <c r="B70">
-        <v>-0.00013304610241822009</v>
+        <v>0.00012078802014172472</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.014167725533587338</v>
       </c>
       <c r="B71">
-        <v>-0.00015678190307392455</v>
+        <v>9.4372315089742679E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.012879750485079397</v>
       </c>
       <c r="B72">
-        <v>-0.00017885470151737185</v>
+        <v>6.7818279772868792E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.011591775436571458</v>
       </c>
       <c r="B73">
-        <v>-0.00020170535169369911</v>
+        <v>3.9498383276695233E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.010303800388063519</v>
       </c>
       <c r="B74">
-        <v>-0.000224329801863092</v>
+        <v>1.0081656965353116E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.00901582533955558</v>
       </c>
       <c r="B75">
-        <v>-0.000244843926454624</v>
+        <v>-1.9176172829688855E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.00772785029104764</v>
       </c>
       <c r="B76">
-        <v>-0.000261288210257872</v>
+        <v>-4.6969162186150696E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0064398752425396987</v>
       </c>
       <c r="B77">
-        <v>-0.0002718483122046245</v>
+        <v>-7.20881714455485E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0051519001940317595</v>
       </c>
       <c r="B78">
-        <v>-0.00027536597743501332</v>
+        <v>-9.376149559539377E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.00386392514552382</v>
       </c>
       <c r="B79">
-        <v>-0.00026986759410692834</v>
+        <v>-0.000110673878111347</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0025759500970158797</v>
       </c>
       <c r="B80">
-        <v>-0.00025189156928145446</v>
+        <v>-0.00012051811433364462</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0012879750485079399</v>
       </c>
       <c r="B81">
-        <v>-0.00021293893019973638</v>
+        <v>-0.00011762877661014885</v>
       </c>
     </row>
     <row r="82" spans="1:2">
